--- a/out/Attention-S4_repeat_4_000007.xlsx
+++ b/out/Attention-S4_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC39" t="n">
-        <v>-4.395924577605911e-05</v>
+        <v>-0.0003171228220087942</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.5067851801537094</v>
+        <v>3.655957777380547</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.01435375873705</v>
+        <v>7.31756700569881</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.07599467572866765</v>
+        <v>0.5482271771255234</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.6588778000452693</v>
+        <v>4.753156784355099</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.09501812846985687</v>
+        <v>0.685462296253635</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.7729314043672939</v>
+        <v>5.575941375612252</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1362080365474098</v>
+        <v>0.9826069509420556</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.9503829719277322</v>
+        <v>6.856080030142436</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1457152709872411</v>
+        <v>1.051195150994249</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.806964148813837</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.105616329433675</v>
+        <v>7.97593631727129</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1544295547199727</v>
+        <v>1.114054981858092</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.268770498092334</v>
+        <v>9.152930673919437</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.069690519981951</v>
+        <v>0.5027516273922944</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.253594985725355</v>
+        <v>9.043454504317664</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03365797900113297</v>
+        <v>0.2428067001549286</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.251164444085628</v>
+        <v>9.025920718491976</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01603689485996011</v>
+        <v>0.1156901638081973</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.249553655775058</v>
+        <v>9.014301523771193</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004747748752647421</v>
+        <v>0.03427818854337265</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.242999319504387</v>
+        <v>8.967044505166792</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00313924252662757</v>
+        <v>0.02267374347003864</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.244527344215416</v>
+        <v>8.978095905512694</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001603766617006291</v>
+        <v>0.01160271852038117</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.244594749492531</v>
+        <v>8.978613189321965</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008184496284424812</v>
+        <v>0.00593329994887799</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.244625940583282</v>
+        <v>8.978869181063212</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003045659311278414</v>
+        <v>0.002227053620772627</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.244415998966155</v>
+        <v>8.97738624680764</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001633012193607549</v>
+        <v>0.001211883816456439</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.244438688532677</v>
+        <v>8.977580960098505</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.606245495694951e-05</v>
+        <v>0.000580715973561488</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.244427375490073</v>
+        <v>8.977530533980623</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.518171098918706e-05</v>
+        <v>0.0003580794383335299</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.244441828003958</v>
+        <v>8.97766490789528</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.176359809462174e-05</v>
+        <v>0.0001844039249773231</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.244439159806378</v>
+        <v>8.977676455350235</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.988210700207309e-06</v>
+        <v>8.691656803223635e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.244433355874358</v>
+        <v>8.977665735672772</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.674878266576269e-06</v>
+        <v>5.384073337708474e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.244431991625113</v>
+        <v>8.977686740497134</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>2.180905938564374e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.244426191676022</v>
+        <v>8.97767636536414</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>7.35242988982542e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.244420643547801</v>
+        <v>8.977668076594815</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>1.675769385467227e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.244415808913483</v>
+        <v>8.977664068788902</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.244415664929575</v>
+        <v>8.977658201346218</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.244415642195274</v>
+        <v>8.97765313199085</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.244415960475491</v>
+        <v>8.977648767016882</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.244417051721948</v>
+        <v>8.977649858263337</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.244416362114812</v>
+        <v>8.977649168656201</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.244416392427213</v>
+        <v>8.977649198968605</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.244416202974703</v>
+        <v>8.977649009516094</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.244416256021406</v>
+        <v>8.977649062562797</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.244416309068109</v>
+        <v>8.977649115609498</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.244416271177607</v>
+        <v>8.977649077718997</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.2444161423499</v>
+        <v>8.977648948891291</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.244415998365993</v>
+        <v>8.977648804907384</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.244415892272587</v>
+        <v>8.977648698813979</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.244415657351475</v>
+        <v>8.977648463892866</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.244415824069683</v>
+        <v>8.977648630611075</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.244416021100294</v>
+        <v>8.977648827641685</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.244415861960186</v>
+        <v>8.977648668501576</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.244415899850688</v>
+        <v>8.977648706392078</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.244416096881298</v>
+        <v>8.97764890342269</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.244416074146997</v>
+        <v>8.977648880688388</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.244415922584989</v>
+        <v>8.977648729126379</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.244415846803985</v>
+        <v>8.977648653345376</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.24441594531929</v>
+        <v>8.977648751860681</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.24441595289739</v>
+        <v>8.977648759438781</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.244416218130904</v>
+        <v>8.977649024672294</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.244415922584989</v>
+        <v>8.977648729126379</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.244416165084201</v>
+        <v>8.977648971625593</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.244416248443305</v>
+        <v>8.977649054984695</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.244416081725097</v>
+        <v>8.977648888266486</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.244416271177607</v>
+        <v>8.977649077718997</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.244415922584989</v>
+        <v>8.977648729126379</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.244415717976278</v>
+        <v>8.977648524517669</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.244415831647784</v>
+        <v>8.977648638189175</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.244415846803985</v>
+        <v>8.977648653345376</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.244415611882872</v>
+        <v>8.977648418424264</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.244415672507675</v>
+        <v>8.977648479049066</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.244415543679969</v>
+        <v>8.97764835022136</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.244415680085776</v>
+        <v>8.977648486627167</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.244415854382085</v>
+        <v>8.977648660923476</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.244415998365993</v>
+        <v>8.977648804907384</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.244415831647784</v>
+        <v>8.977648638189175</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.244415824069683</v>
+        <v>8.977648630611075</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.244415536101868</v>
+        <v>8.97764834264326</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.244415551258069</v>
+        <v>8.97764835779946</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.244415778601081</v>
+        <v>8.977648585142473</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.4694694960034209</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.24441576344488</v>
+        <v>8.97764856998627</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.244415869538286</v>
+        <v>8.977648676079678</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.244415596726672</v>
+        <v>8.977648403268061</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.244415695241977</v>
+        <v>8.977648501783367</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.244415846803985</v>
+        <v>8.977648653345376</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.244415861960186</v>
+        <v>8.977648668501576</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.244415922584989</v>
+        <v>8.977648729126379</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.244416021100294</v>
+        <v>8.977648827641685</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.244415854382085</v>
+        <v>8.977648660923476</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.244415808913483</v>
+        <v>8.977648615454873</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.244415793757282</v>
+        <v>8.977648600298673</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.244415831647784</v>
+        <v>8.977648638189175</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.244415846803985</v>
+        <v>8.977648653345376</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.244415839225884</v>
+        <v>8.977648645767275</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000007.xlsx
+++ b/out/Attention-S4_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC39" t="n">
-        <v>-4.395924577605911e-05</v>
+        <v>-7.420911434385926e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.5067851801537094</v>
+        <v>0.8555214128920784</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.01435375873705</v>
+        <v>1.712365459049056</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.07599467572866765</v>
+        <v>0.1282892748425815</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.6588778000452693</v>
+        <v>1.112274216911013</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.09501812846985687</v>
+        <v>0.1604033361837382</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.7729314043672939</v>
+        <v>1.304811987667427</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1362080365474098</v>
+        <v>0.2299374217223412</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.9503829719277322</v>
+        <v>1.604374017630563</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1457152709872411</v>
+        <v>0.2459871472279488</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.105616329433675</v>
+        <v>1.866428730737467</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1544295547199727</v>
+        <v>0.2606975328024075</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.268770498092334</v>
+        <v>2.141854566892126</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.069690519981951</v>
+        <v>0.1176472820363745</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.253594985725355</v>
+        <v>2.116236292283976</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03365797900113297</v>
+        <v>0.05681825997321122</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1348825055873001</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.251164444085628</v>
+        <v>2.112133233180566</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01603689485996011</v>
+        <v>0.02707282218550377</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.249553655775058</v>
+        <v>2.109414208656268</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004747748752647421</v>
+        <v>0.008018941977600591</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.242999319504387</v>
+        <v>2.098352979145568</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00313924252662757</v>
+        <v>0.005302050745799698</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.244527344215416</v>
+        <v>2.100935749814033</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001603766617006291</v>
+        <v>0.002711700079238146</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.244594749492531</v>
+        <v>2.101052981129452</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008184496284424812</v>
+        <v>0.001384193749695139</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.244625940583282</v>
+        <v>2.101109059738125</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003045659311278414</v>
+        <v>0.0005172505928562605</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.244415998966155</v>
+        <v>2.100758064634363</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001633012193607549</v>
+        <v>0.0002796270621542178</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.244438688532677</v>
+        <v>2.100799845437502</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.606245495694951e-05</v>
+        <v>0.0001324882814465908</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.244427375490073</v>
+        <v>2.100784189434317</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.518171098918706e-05</v>
+        <v>7.962014009941348e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.244441828003958</v>
+        <v>2.100811861696205</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.176359809462174e-05</v>
+        <v>3.926287377187443e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.244439159806378</v>
+        <v>2.100810763607269</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.988210700207309e-06</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.244433355874358</v>
+        <v>2.100804403106928</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.674878266576269e-06</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.244431991625113</v>
+        <v>2.10080555460217</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.244426191676022</v>
+        <v>2.100799297134689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.244420643547801</v>
+        <v>2.100793474942358</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.244415808913483</v>
+        <v>2.100788723667144</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.244415664929575</v>
+        <v>2.100783434519582</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.244415642195274</v>
+        <v>2.100783411785281</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.244415960475491</v>
+        <v>2.100783730065497</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.244417051721948</v>
+        <v>2.100784821311954</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.244416362114812</v>
+        <v>2.100784131704819</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.244416392427213</v>
+        <v>2.10078416201722</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.244416202974703</v>
+        <v>2.10078397256471</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.244416256021406</v>
+        <v>2.100784025611413</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.244416309068109</v>
+        <v>2.100784078658116</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.244416271177607</v>
+        <v>2.100784040767613</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.2444161423499</v>
+        <v>2.100783911939907</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.244415998365993</v>
+        <v>2.100783767956</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.244415892272587</v>
+        <v>2.100783661862593</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.244415657351475</v>
+        <v>2.100783426941482</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.244415824069683</v>
+        <v>2.10078359365969</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.244416021100294</v>
+        <v>2.100783790690301</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.244415861960186</v>
+        <v>2.100783631550192</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.244415899850688</v>
+        <v>2.100783669440694</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.244416096881298</v>
+        <v>2.100783866471305</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.244416074146997</v>
+        <v>2.100783843737003</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.244415922584989</v>
+        <v>2.100783692174995</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.244415846803985</v>
+        <v>2.100783616393991</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.24441594531929</v>
+        <v>2.100783714909296</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.24441595289739</v>
+        <v>2.100783722487397</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.244416218130904</v>
+        <v>2.100783987720911</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.244415922584989</v>
+        <v>2.100783692174995</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.244416165084201</v>
+        <v>2.100783934674208</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.244416248443305</v>
+        <v>2.100784018033312</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.244416081725097</v>
+        <v>2.100783851315104</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.244416271177607</v>
+        <v>2.100784040767613</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.244415922584989</v>
+        <v>2.100783692174995</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.244415717976278</v>
+        <v>2.100783487566285</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.244415831647784</v>
+        <v>2.100783601237791</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.244415846803985</v>
+        <v>2.100783616393991</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.244415611882872</v>
+        <v>2.100783381472879</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.244415672507675</v>
+        <v>2.100783442097682</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.244415543679969</v>
+        <v>2.100783313269976</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.244415680085776</v>
+        <v>2.100783449675783</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.244415854382085</v>
+        <v>2.100783623972092</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.244415998365993</v>
+        <v>2.100783767956</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.244415831647784</v>
+        <v>2.100783601237791</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.244415824069683</v>
+        <v>2.10078359365969</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.244415536101868</v>
+        <v>2.100783305691875</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.244415551258069</v>
+        <v>2.100783320848076</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.244415778601081</v>
+        <v>2.100783548191088</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.24441576344488</v>
+        <v>2.100783533034887</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.244415869538286</v>
+        <v>2.100783639128292</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.244415596726672</v>
+        <v>2.100783366316679</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.244415695241977</v>
+        <v>2.100783464831984</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.244415846803985</v>
+        <v>2.100783616393991</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.244415861960186</v>
+        <v>2.100783631550192</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.244415922584989</v>
+        <v>2.100783692174995</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.244416021100294</v>
+        <v>2.100783790690301</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.244415854382085</v>
+        <v>2.100783623972092</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.244415808913483</v>
+        <v>2.100783578503489</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.244415793757282</v>
+        <v>2.100783563347288</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.244415831647784</v>
+        <v>2.100783601237791</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.244415846803985</v>
+        <v>2.100783616393991</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.244415839225884</v>
+        <v>2.100783608815891</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000007.xlsx
+++ b/out/Attention-S4_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.001604663208127022</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.0002942774444818497</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7211965688743771</v>
+        <v>0.04999999999999988</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.002250110730528831</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0007808450609445572</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.003020366653800011</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.00346052460372448</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001978671178221703</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.002176817506551743</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001582583412528038</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003347916528582573</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.004181193187832832</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.003534659743309021</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.004533072933554649</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.005063753575086594</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.005353817716240883</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.004983687773346901</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.00566381961107254</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.00612281821668148</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.006088398396968842</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.006038958206772804</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.007102830335497856</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.007185084745287895</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008066954091191292</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.007598167285323143</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.007330179214477539</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.007071932777762413</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.006720660254359245</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.007512079551815987</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.009187715128064156</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.008869761601090431</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.008518936112523079</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.008516469970345497</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.007614666596055031</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.007691590115427971</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.008265653625130653</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0001913607120513916</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.005929028615355492</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004823295399546623</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-7.420911434385926e-05</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.8555214128920784</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.004492510110139847</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.712365459049056</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1282892748425815</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.004608228802680969</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.112274216911013</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1604033361837382</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.004867082461714745</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.304811987667427</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2299374217223412</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0006195977330207825</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.604374017630563</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2459871472279488</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001225631684064865</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.866428730737467</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2606975328024075</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006406655535101891</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.141854566892126</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1176472820363745</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01392783410847187</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.980598284437189</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.116236292283976</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05681825997321122</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002543281763792038</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.112133233180566</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02707282218550377</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.006554460152983665</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.109414208656268</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008018941977600591</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.003533573821187019</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.098352979145568</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005302050745799698</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001468377187848091</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.100935749814033</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002711700079238146</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003732258453965187</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.101052981129452</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001384193749695139</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002175742760300636</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.101109059738125</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005172505928562605</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003425763919949532</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.100758064634363</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002796270621542178</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.004334956407546997</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.100799845437502</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001324882814465908</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.005073117092251778</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.100784189434317</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.962014009941348e-05</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.004277974367141724</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.100811861696205</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.926287377187443e-05</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.00303962267935276</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.100810763607269</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.698004887727391e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.010900704190135</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.100804403106928</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.070610155389825e-06</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-8.122250437736511e-05</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.10080555460217</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004789890721440315</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.100799297134689</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004854964092373848</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.100793474942358</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00354386679828167</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.100788723667144</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003746109083294868</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.100783434519582</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001266801729798317</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7211965688743771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.100783411785281</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.007408769801259041</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.980598284437189</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.100783730065497</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03783662617206573</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.04</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.100784821311954</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01214092783629894</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.04</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.100784131704819</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.000267835333943367</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.980598284437189</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.10078416201722</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001838792115449905</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.10078397256471</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002059182152152061</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.100784025611413</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004143914207816124</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.100784078658116</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.004686258733272552</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.100784040767613</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004275484010577202</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.100783911939907</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004696808755397797</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.100783767956</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00517372228205204</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004858719184994698</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.100783661862593</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.006769120693206787</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.005445787683129311</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004342058673501015</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.100783426941482</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003293192014098167</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.10078359365969</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006024403497576714</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.100783790690301</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005003735423088074</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.100783631550192</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004952700808644295</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.100783669440694</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003852277994155884</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.100783866471305</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.00538351945579052</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.100783843737003</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005936611443758011</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.100783692174995</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006082260981202126</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.100783616393991</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005296410992741585</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.100783714909296</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003685250878334045</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.100783722487397</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003933681175112724</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.100783987720911</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004481140524148941</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.100783692174995</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003319656476378441</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.100783934674208</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002936521545052528</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.100784018033312</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0004343185573816299</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.100783851315104</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003042632713913918</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.100784040767613</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003761777654290199</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.100783692174995</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004809532314538956</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.100783487566285</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004977602511644363</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.100783601237791</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003758331760764122</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.100783616393991</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00486830435693264</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.100783381472879</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004495525732636452</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.100783442097682</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001635340973734856</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.100783313269976</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.0008843094110488892</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.100783449675783</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004462938755750656</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.100783623972092</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00427018478512764</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.100783767956</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003786943852901459</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.100783601237791</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003457149490714073</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.10078359365969</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005812088027596474</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.100783305691875</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.006684450432658195</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.100783320848076</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.00594617985188961</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.100783548191088</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005069037899374962</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.100783533034887</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00516880489885807</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.100783639128292</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005822509527206421</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.100783366316679</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.005075855180621147</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.100783464831984</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003541285172104836</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.100783616393991</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004144042730331421</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.100783631550192</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003261381760239601</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.001924777403473854</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.100783692174995</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003467248752713203</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.100783790690301</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003428636118769646</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.100783623972092</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002352507784962654</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002138679847121239</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.100783578503489</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002245837822556496</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.100783563347288</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002471698448061943</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.100783601237791</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004223106428980827</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.09000000000000014</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.100783616393991</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0008004046976566315</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.100783608815891</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000007.xlsx
+++ b/out/Attention-S4_repeat_4_000007.xlsx
@@ -53414,7 +53414,7 @@
         <v>0.03783662617206573</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>4.68754321864965</v>
@@ -54209,7 +54209,7 @@
         <v>0.01214092783629894</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>4.687542529042514</v>
@@ -55004,7 +55004,7 @@
         <v>0.000267835333943367</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>4.687542559354916</v>
@@ -55799,7 +55799,7 @@
         <v>-0.001838792115449905</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>4.687542369902406</v>
@@ -56594,7 +56594,7 @@
         <v>-0.002059182152152061</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>4.687542422949109</v>
@@ -73289,7 +73289,7 @@
         <v>-0.004481140524148941</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>4.687542089512691</v>
@@ -74084,7 +74084,7 @@
         <v>-0.003319656476378441</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>4.687542332011904</v>
@@ -74879,7 +74879,7 @@
         <v>-0.002936521545052528</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>4.687542415371008</v>
@@ -75674,7 +75674,7 @@
         <v>0.0004343185573816299</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>4.6875422486528</v>
@@ -76469,7 +76469,7 @@
         <v>-0.003042632713913918</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
         <v>4.687542438105309</v>
@@ -77264,7 +77264,7 @@
         <v>-0.003761777654290199</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
         <v>4.687542089512691</v>
@@ -78059,7 +78059,7 @@
         <v>-0.004809532314538956</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>4.687541884903981</v>
@@ -79649,7 +79649,7 @@
         <v>-0.003758331760764122</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>4.687542013731687</v>
@@ -80444,7 +80444,7 @@
         <v>-0.00486830435693264</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
         <v>4.687541778810576</v>
